--- a/outputs/marine_equipment/Отгрузка_учет_образец.xlsx
+++ b/outputs/marine_equipment/Отгрузка_учет_образец.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Итоги по состоянию" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Отгрузка'!$A$4:$Y$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Отгрузка'!$A$4:$Y$250</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>SUM('Отгрузка'!N5:N229)</f>
+        <f>SUM('Отгрузка'!N5:N250)</f>
         <v/>
       </c>
     </row>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B20" s="13">
-        <f>SUM('Отгрузка'!O5:O229)</f>
+        <f>SUM('Отгрузка'!O5:O250)</f>
         <v/>
       </c>
     </row>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>SUM('Отгрузка'!L5:L229)</f>
+        <f>SUM('Отгрузка'!L5:L250)</f>
         <v/>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>SUM('Отгрузка'!T5:T229)</f>
+        <f>SUM('Отгрузка'!T5:T250)</f>
         <v/>
       </c>
     </row>
@@ -956,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y230"/>
+  <dimension ref="A1:Y251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -13658,7 +13658,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -14942,7 +14942,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -17566,7 +17566,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -17742,7 +17742,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -18466,7 +18466,7 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -18562,7 +18562,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -18654,7 +18654,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -19994,7 +19994,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -20346,7 +20346,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -20978,25 +20978,29 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
-        </is>
-      </c>
-      <c r="G222" s="4" t="inlineStr"/>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>527-03.054</t>
+        </is>
+      </c>
       <c r="H222" s="16" t="inlineStr"/>
       <c r="I222" s="16" t="inlineStr">
         <is>
@@ -21011,14 +21015,14 @@
         <v>1</v>
       </c>
       <c r="M222" s="16" t="n">
-        <v>1.5</v>
+        <v>20</v>
       </c>
       <c r="N222" s="17">
         <f>L222*M222</f>
         <v/>
       </c>
       <c r="O222" s="18" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="P222" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N222/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O222/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L222/'Расходы и доставка'!$B$21,T222/'Расходы и доставка'!$B$22))),0)</f>
@@ -21033,7 +21037,7 @@
         <v/>
       </c>
       <c r="S222" s="21" t="n">
-        <v>1000</v>
+        <v>17500</v>
       </c>
       <c r="T222" s="17">
         <f>L222*S222</f>
@@ -21050,7 +21054,7 @@
       <c r="W222" s="16" t="inlineStr"/>
       <c r="X222" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y222" s="23" t="inlineStr"/>
@@ -21066,33 +21070,29 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
-        </is>
-      </c>
-      <c r="G223" s="4" t="inlineStr">
-        <is>
-          <t>521-03.124</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr"/>
       <c r="H223" s="16" t="inlineStr"/>
       <c r="I223" s="16" t="inlineStr">
         <is>
-          <t>Комплект</t>
+          <t>Не комплект</t>
         </is>
       </c>
       <c r="J223" s="4" t="inlineStr"/>
@@ -21103,14 +21103,14 @@
         <v>2</v>
       </c>
       <c r="M223" s="16" t="n">
-        <v>2.5</v>
+        <v>28</v>
       </c>
       <c r="N223" s="17">
         <f>L223*M223</f>
         <v/>
       </c>
       <c r="O223" s="18" t="n">
-        <v>0.006</v>
+        <v>0.06</v>
       </c>
       <c r="P223" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N223/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O223/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L223/'Расходы и доставка'!$B$21,T223/'Расходы и доставка'!$B$22))),0)</f>
@@ -21125,7 +21125,7 @@
         <v/>
       </c>
       <c r="S223" s="21" t="n">
-        <v>1250</v>
+        <v>24000</v>
       </c>
       <c r="T223" s="17">
         <f>L223*S223</f>
@@ -21142,7 +21142,7 @@
       <c r="W223" s="16" t="inlineStr"/>
       <c r="X223" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y223" s="23" t="inlineStr"/>
@@ -21158,22 +21158,22 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+          <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr"/>
@@ -21185,20 +21185,20 @@
       </c>
       <c r="J224" s="4" t="inlineStr"/>
       <c r="K224" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L224" s="16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M224" s="16" t="n">
-        <v>3.5</v>
+        <v>40</v>
       </c>
       <c r="N224" s="17">
         <f>L224*M224</f>
         <v/>
       </c>
       <c r="O224" s="18" t="n">
-        <v>0.005</v>
+        <v>0.225</v>
       </c>
       <c r="P224" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N224/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O224/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L224/'Расходы и доставка'!$B$21,T224/'Расходы и доставка'!$B$22))),0)</f>
@@ -21213,7 +21213,7 @@
         <v/>
       </c>
       <c r="S224" s="21" t="n">
-        <v>1500</v>
+        <v>34000</v>
       </c>
       <c r="T224" s="17">
         <f>L224*S224</f>
@@ -21230,7 +21230,7 @@
       <c r="W224" s="16" t="inlineStr"/>
       <c r="X224" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y224" s="23" t="inlineStr"/>
@@ -21246,29 +21246,25 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>Ду15</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
-        </is>
-      </c>
-      <c r="G225" s="4" t="inlineStr">
-        <is>
-          <t>521-35.2608-01</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду125</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr"/>
       <c r="H225" s="16" t="inlineStr"/>
       <c r="I225" s="16" t="inlineStr">
         <is>
@@ -21277,20 +21273,20 @@
       </c>
       <c r="J225" s="4" t="inlineStr"/>
       <c r="K225" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L225" s="16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M225" s="16" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="N225" s="17">
         <f>L225*M225</f>
         <v/>
       </c>
       <c r="O225" s="18" t="n">
-        <v>0.005</v>
+        <v>0.42</v>
       </c>
       <c r="P225" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N225/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O225/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L225/'Расходы и доставка'!$B$21,T225/'Расходы и доставка'!$B$22))),0)</f>
@@ -21304,7 +21300,9 @@
         <f>IFERROR(Q225/L225,0)</f>
         <v/>
       </c>
-      <c r="S225" s="21" t="n"/>
+      <c r="S225" s="21" t="n">
+        <v>46000</v>
+      </c>
       <c r="T225" s="17">
         <f>L225*S225</f>
         <v/>
@@ -21320,7 +21318,7 @@
       <c r="W225" s="16" t="inlineStr"/>
       <c r="X225" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y225" s="23" t="inlineStr"/>
@@ -21336,29 +21334,25 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>Ду15</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
-        </is>
-      </c>
-      <c r="G226" s="4" t="inlineStr">
-        <is>
-          <t>528-35.176</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду125 Ру10</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="inlineStr"/>
       <c r="H226" s="16" t="inlineStr"/>
       <c r="I226" s="16" t="inlineStr">
         <is>
@@ -21367,20 +21361,20 @@
       </c>
       <c r="J226" s="4" t="inlineStr"/>
       <c r="K226" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L226" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M226" s="16" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="N226" s="17">
         <f>L226*M226</f>
         <v/>
       </c>
       <c r="O226" s="18" t="n">
-        <v>0.002</v>
+        <v>0.21</v>
       </c>
       <c r="P226" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N226/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O226/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L226/'Расходы и доставка'!$B$21,T226/'Расходы и доставка'!$B$22))),0)</f>
@@ -21394,7 +21388,9 @@
         <f>IFERROR(Q226/L226,0)</f>
         <v/>
       </c>
-      <c r="S226" s="21" t="n"/>
+      <c r="S226" s="21" t="n">
+        <v>46000</v>
+      </c>
       <c r="T226" s="17">
         <f>L226*S226</f>
         <v/>
@@ -21410,7 +21406,7 @@
       <c r="W226" s="16" t="inlineStr"/>
       <c r="X226" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y226" s="23" t="inlineStr"/>
@@ -21426,25 +21422,25 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="E227" s="4" t="inlineStr"/>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>Клапан дроссельный угловой штуцерный</t>
-        </is>
-      </c>
-      <c r="G227" s="4" t="inlineStr">
-        <is>
-          <t>525-35.577</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (521-35.3437)</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr"/>
       <c r="H227" s="16" t="inlineStr"/>
       <c r="I227" s="16" t="inlineStr">
         <is>
@@ -21459,14 +21455,14 @@
         <v>1</v>
       </c>
       <c r="M227" s="16" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="N227" s="17">
         <f>L227*M227</f>
         <v/>
       </c>
       <c r="O227" s="18" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="P227" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N227/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O227/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L227/'Расходы и доставка'!$B$21,T227/'Расходы и доставка'!$B$22))),0)</f>
@@ -21480,7 +21476,9 @@
         <f>IFERROR(Q227/L227,0)</f>
         <v/>
       </c>
-      <c r="S227" s="21" t="n"/>
+      <c r="S227" s="21" t="n">
+        <v>22000</v>
+      </c>
       <c r="T227" s="17">
         <f>L227*S227</f>
         <v/>
@@ -21496,7 +21494,7 @@
       <c r="W227" s="16" t="inlineStr"/>
       <c r="X227" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y227" s="23" t="inlineStr"/>
@@ -21512,29 +21510,25 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
-        </is>
-      </c>
-      <c r="G228" s="4" t="inlineStr">
-        <is>
-          <t>521-01.493-02</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (522-01.101)</t>
+        </is>
+      </c>
+      <c r="G228" s="4" t="inlineStr"/>
       <c r="H228" s="16" t="inlineStr"/>
       <c r="I228" s="16" t="inlineStr">
         <is>
@@ -21549,14 +21543,14 @@
         <v>1</v>
       </c>
       <c r="M228" s="16" t="n">
-        <v>0.6</v>
+        <v>28</v>
       </c>
       <c r="N228" s="17">
         <f>L228*M228</f>
         <v/>
       </c>
       <c r="O228" s="18" t="n">
-        <v>0.001</v>
+        <v>0.03</v>
       </c>
       <c r="P228" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N228/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O228/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L228/'Расходы и доставка'!$B$21,T228/'Расходы и доставка'!$B$22))),0)</f>
@@ -21570,7 +21564,9 @@
         <f>IFERROR(Q228/L228,0)</f>
         <v/>
       </c>
-      <c r="S228" s="21" t="n"/>
+      <c r="S228" s="21" t="n">
+        <v>22000</v>
+      </c>
       <c r="T228" s="17">
         <f>L228*S228</f>
         <v/>
@@ -21586,7 +21582,7 @@
       <c r="W228" s="16" t="inlineStr"/>
       <c r="X228" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y228" s="23" t="inlineStr"/>
@@ -21602,25 +21598,25 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="E229" s="4" t="inlineStr"/>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
-        </is>
-      </c>
-      <c r="G229" s="4" t="inlineStr">
-        <is>
-          <t>521-03.472-01</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная ДУ 80, сталь</t>
+        </is>
+      </c>
+      <c r="G229" s="4" t="inlineStr"/>
       <c r="H229" s="16" t="inlineStr"/>
       <c r="I229" s="16" t="inlineStr">
         <is>
@@ -21635,14 +21631,14 @@
         <v>1</v>
       </c>
       <c r="M229" s="16" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="N229" s="17">
         <f>L229*M229</f>
         <v/>
       </c>
       <c r="O229" s="18" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="P229" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N229/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O229/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L229/'Расходы и доставка'!$B$21,T229/'Расходы и доставка'!$B$22))),0)</f>
@@ -21656,7 +21652,9 @@
         <f>IFERROR(Q229/L229,0)</f>
         <v/>
       </c>
-      <c r="S229" s="21" t="n"/>
+      <c r="S229" s="21" t="n">
+        <v>22000</v>
+      </c>
       <c r="T229" s="17">
         <f>L229*S229</f>
         <v/>
@@ -21672,49 +21670,1915 @@
       <c r="W229" s="16" t="inlineStr"/>
       <c r="X229" s="4" t="inlineStr">
         <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="Y229" s="23" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="n">
+        <v>226</v>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+        </is>
+      </c>
+      <c r="G230" s="4" t="inlineStr"/>
+      <c r="H230" s="16" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="I230" s="16" t="inlineStr">
+        <is>
+          <t>Не комплект</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="inlineStr"/>
+      <c r="K230" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="N230" s="17">
+        <f>L230*M230</f>
+        <v/>
+      </c>
+      <c r="O230" s="18" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="P230" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N230/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O230/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L230/'Расходы и доставка'!$B$21,T230/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q230" s="17">
+        <f>P230*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R230" s="20">
+        <f>IFERROR(Q230/L230,0)</f>
+        <v/>
+      </c>
+      <c r="S230" s="21" t="n">
+        <v>35000</v>
+      </c>
+      <c r="T230" s="17">
+        <f>L230*S230</f>
+        <v/>
+      </c>
+      <c r="U230" s="17">
+        <f>S230+R230</f>
+        <v/>
+      </c>
+      <c r="V230" s="22">
+        <f>IFERROR(R230/S230,"")</f>
+        <v/>
+      </c>
+      <c r="W230" s="16" t="inlineStr"/>
+      <c r="X230" s="4" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="Y230" s="23" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t>Ду125</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
+        </is>
+      </c>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>521-35.3455-02</t>
+        </is>
+      </c>
+      <c r="H231" s="16" t="inlineStr"/>
+      <c r="I231" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J231" s="4" t="inlineStr"/>
+      <c r="K231" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L231" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M231" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="N231" s="17">
+        <f>L231*M231</f>
+        <v/>
+      </c>
+      <c r="O231" s="18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P231" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N231/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O231/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L231/'Расходы и доставка'!$B$21,T231/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q231" s="17">
+        <f>P231*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R231" s="20">
+        <f>IFERROR(Q231/L231,0)</f>
+        <v/>
+      </c>
+      <c r="S231" s="21" t="n">
+        <v>37500</v>
+      </c>
+      <c r="T231" s="17">
+        <f>L231*S231</f>
+        <v/>
+      </c>
+      <c r="U231" s="17">
+        <f>S231+R231</f>
+        <v/>
+      </c>
+      <c r="V231" s="22">
+        <f>IFERROR(R231/S231,"")</f>
+        <v/>
+      </c>
+      <c r="W231" s="16" t="inlineStr"/>
+      <c r="X231" s="4" t="inlineStr">
+        <is>
           <t>Склад 2</t>
         </is>
       </c>
-      <c r="Y229" s="23" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="F230" s="9" t="inlineStr">
+      <c r="Y231" s="23" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+        </is>
+      </c>
+      <c r="G232" s="4" t="inlineStr"/>
+      <c r="H232" s="16" t="inlineStr"/>
+      <c r="I232" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J232" s="4" t="inlineStr"/>
+      <c r="K232" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L232" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N232" s="17">
+        <f>L232*M232</f>
+        <v/>
+      </c>
+      <c r="O232" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P232" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N232/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O232/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L232/'Расходы и доставка'!$B$21,T232/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q232" s="17">
+        <f>P232*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R232" s="20">
+        <f>IFERROR(Q232/L232,0)</f>
+        <v/>
+      </c>
+      <c r="S232" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T232" s="17">
+        <f>L232*S232</f>
+        <v/>
+      </c>
+      <c r="U232" s="17">
+        <f>S232+R232</f>
+        <v/>
+      </c>
+      <c r="V232" s="22">
+        <f>IFERROR(R232/S232,"")</f>
+        <v/>
+      </c>
+      <c r="W232" s="16" t="inlineStr"/>
+      <c r="X232" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y232" s="23" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>Клинкет Ду 100, сталь</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr"/>
+      <c r="H233" s="16" t="inlineStr"/>
+      <c r="I233" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="inlineStr"/>
+      <c r="K233" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L233" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M233" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="N233" s="17">
+        <f>L233*M233</f>
+        <v/>
+      </c>
+      <c r="O233" s="18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P233" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N233/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O233/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L233/'Расходы и доставка'!$B$21,T233/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q233" s="17">
+        <f>P233*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R233" s="20">
+        <f>IFERROR(Q233/L233,0)</f>
+        <v/>
+      </c>
+      <c r="S233" s="21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T233" s="17">
+        <f>L233*S233</f>
+        <v/>
+      </c>
+      <c r="U233" s="17">
+        <f>S233+R233</f>
+        <v/>
+      </c>
+      <c r="V233" s="22">
+        <f>IFERROR(R233/S233,"")</f>
+        <v/>
+      </c>
+      <c r="W233" s="16" t="inlineStr"/>
+      <c r="X233" s="4" t="inlineStr">
+        <is>
+          <t>Фойе</t>
+        </is>
+      </c>
+      <c r="Y233" s="23" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>Ду125</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
+        </is>
+      </c>
+      <c r="G234" s="4" t="inlineStr"/>
+      <c r="H234" s="16" t="inlineStr"/>
+      <c r="I234" s="16" t="inlineStr">
+        <is>
+          <t>Не комплект</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="inlineStr"/>
+      <c r="K234" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L234" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="N234" s="17">
+        <f>L234*M234</f>
+        <v/>
+      </c>
+      <c r="O234" s="18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P234" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N234/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O234/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L234/'Расходы и доставка'!$B$21,T234/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q234" s="17">
+        <f>P234*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R234" s="20">
+        <f>IFERROR(Q234/L234,0)</f>
+        <v/>
+      </c>
+      <c r="S234" s="21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T234" s="17">
+        <f>L234*S234</f>
+        <v/>
+      </c>
+      <c r="U234" s="17">
+        <f>S234+R234</f>
+        <v/>
+      </c>
+      <c r="V234" s="22">
+        <f>IFERROR(R234/S234,"")</f>
+        <v/>
+      </c>
+      <c r="W234" s="16" t="inlineStr"/>
+      <c r="X234" s="4" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="Y234" s="23" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>Ду50</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+        </is>
+      </c>
+      <c r="G235" s="4" t="inlineStr"/>
+      <c r="H235" s="16" t="inlineStr"/>
+      <c r="I235" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J235" s="4" t="inlineStr"/>
+      <c r="K235" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L235" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M235" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="N235" s="17">
+        <f>L235*M235</f>
+        <v/>
+      </c>
+      <c r="O235" s="18" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="P235" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N235/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O235/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L235/'Расходы и доставка'!$B$21,T235/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q235" s="17">
+        <f>P235*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R235" s="20">
+        <f>IFERROR(Q235/L235,0)</f>
+        <v/>
+      </c>
+      <c r="S235" s="21" t="n">
+        <v>7500</v>
+      </c>
+      <c r="T235" s="17">
+        <f>L235*S235</f>
+        <v/>
+      </c>
+      <c r="U235" s="17">
+        <f>S235+R235</f>
+        <v/>
+      </c>
+      <c r="V235" s="22">
+        <f>IFERROR(R235/S235,"")</f>
+        <v/>
+      </c>
+      <c r="W235" s="16" t="inlineStr"/>
+      <c r="X235" s="4" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="Y235" s="23" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="n">
+        <v>232</v>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>коробка клапанная</t>
+        </is>
+      </c>
+      <c r="E236" s="4" t="inlineStr"/>
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>Коробка 2-х клапанная корпус</t>
+        </is>
+      </c>
+      <c r="G236" s="4" t="inlineStr"/>
+      <c r="H236" s="16" t="inlineStr"/>
+      <c r="I236" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J236" s="4" t="inlineStr"/>
+      <c r="K236" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L236" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M236" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="N236" s="17">
+        <f>L236*M236</f>
+        <v/>
+      </c>
+      <c r="O236" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P236" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N236/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O236/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L236/'Расходы и доставка'!$B$21,T236/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q236" s="17">
+        <f>P236*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R236" s="20">
+        <f>IFERROR(Q236/L236,0)</f>
+        <v/>
+      </c>
+      <c r="S236" s="21" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T236" s="17">
+        <f>L236*S236</f>
+        <v/>
+      </c>
+      <c r="U236" s="17">
+        <f>S236+R236</f>
+        <v/>
+      </c>
+      <c r="V236" s="22">
+        <f>IFERROR(R236/S236,"")</f>
+        <v/>
+      </c>
+      <c r="W236" s="16" t="inlineStr"/>
+      <c r="X236" s="4" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="Y236" s="23" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="n">
+        <v>233</v>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E237" s="4" t="inlineStr">
+        <is>
+          <t>Ду25</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+        </is>
+      </c>
+      <c r="G237" s="4" t="inlineStr">
+        <is>
+          <t>521-03.124</t>
+        </is>
+      </c>
+      <c r="H237" s="16" t="inlineStr"/>
+      <c r="I237" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J237" s="4" t="inlineStr"/>
+      <c r="K237" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L237" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M237" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N237" s="17">
+        <f>L237*M237</f>
+        <v/>
+      </c>
+      <c r="O237" s="18" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P237" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N237/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O237/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L237/'Расходы и доставка'!$B$21,T237/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q237" s="17">
+        <f>P237*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R237" s="20">
+        <f>IFERROR(Q237/L237,0)</f>
+        <v/>
+      </c>
+      <c r="S237" s="21" t="n">
+        <v>1250</v>
+      </c>
+      <c r="T237" s="17">
+        <f>L237*S237</f>
+        <v/>
+      </c>
+      <c r="U237" s="17">
+        <f>S237+R237</f>
+        <v/>
+      </c>
+      <c r="V237" s="22">
+        <f>IFERROR(R237/S237,"")</f>
+        <v/>
+      </c>
+      <c r="W237" s="16" t="inlineStr"/>
+      <c r="X237" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y237" s="23" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>Ду65</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+        </is>
+      </c>
+      <c r="G238" s="4" t="inlineStr"/>
+      <c r="H238" s="16" t="inlineStr"/>
+      <c r="I238" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J238" s="4" t="inlineStr"/>
+      <c r="K238" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L238" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M238" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="N238" s="17">
+        <f>L238*M238</f>
+        <v/>
+      </c>
+      <c r="O238" s="18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P238" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N238/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O238/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L238/'Расходы и доставка'!$B$21,T238/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q238" s="17">
+        <f>P238*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R238" s="20">
+        <f>IFERROR(Q238/L238,0)</f>
+        <v/>
+      </c>
+      <c r="S238" s="21" t="n">
+        <v>9750</v>
+      </c>
+      <c r="T238" s="17">
+        <f>L238*S238</f>
+        <v/>
+      </c>
+      <c r="U238" s="17">
+        <f>S238+R238</f>
+        <v/>
+      </c>
+      <c r="V238" s="22">
+        <f>IFERROR(R238/S238,"")</f>
+        <v/>
+      </c>
+      <c r="W238" s="16" t="inlineStr"/>
+      <c r="X238" s="4" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="Y238" s="23" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>Ду65</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+        </is>
+      </c>
+      <c r="G239" s="4" t="inlineStr"/>
+      <c r="H239" s="16" t="inlineStr"/>
+      <c r="I239" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="inlineStr"/>
+      <c r="K239" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L239" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="N239" s="17">
+        <f>L239*M239</f>
+        <v/>
+      </c>
+      <c r="O239" s="18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P239" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N239/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O239/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L239/'Расходы и доставка'!$B$21,T239/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q239" s="17">
+        <f>P239*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R239" s="20">
+        <f>IFERROR(Q239/L239,0)</f>
+        <v/>
+      </c>
+      <c r="S239" s="21" t="n">
+        <v>9750</v>
+      </c>
+      <c r="T239" s="17">
+        <f>L239*S239</f>
+        <v/>
+      </c>
+      <c r="U239" s="17">
+        <f>S239+R239</f>
+        <v/>
+      </c>
+      <c r="V239" s="22">
+        <f>IFERROR(R239/S239,"")</f>
+        <v/>
+      </c>
+      <c r="W239" s="16" t="inlineStr"/>
+      <c r="X239" s="4" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="Y239" s="23" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>Ду32</t>
+        </is>
+      </c>
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+        </is>
+      </c>
+      <c r="G240" s="4" t="inlineStr"/>
+      <c r="H240" s="16" t="inlineStr"/>
+      <c r="I240" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J240" s="4" t="inlineStr"/>
+      <c r="K240" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L240" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" s="16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N240" s="17">
+        <f>L240*M240</f>
+        <v/>
+      </c>
+      <c r="O240" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P240" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N240/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O240/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L240/'Расходы и доставка'!$B$21,T240/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q240" s="17">
+        <f>P240*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R240" s="20">
+        <f>IFERROR(Q240/L240,0)</f>
+        <v/>
+      </c>
+      <c r="S240" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="T240" s="17">
+        <f>L240*S240</f>
+        <v/>
+      </c>
+      <c r="U240" s="17">
+        <f>S240+R240</f>
+        <v/>
+      </c>
+      <c r="V240" s="22">
+        <f>IFERROR(R240/S240,"")</f>
+        <v/>
+      </c>
+      <c r="W240" s="16" t="inlineStr"/>
+      <c r="X240" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y240" s="23" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="n">
+        <v>237</v>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 1, на настил</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>Ду300</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>Задвижка клинкетная стальная Ду300</t>
+        </is>
+      </c>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>544-03.067</t>
+        </is>
+      </c>
+      <c r="H241" s="16" t="inlineStr"/>
+      <c r="I241" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J241" s="4" t="inlineStr"/>
+      <c r="K241" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L241" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M241" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="N241" s="17">
+        <f>L241*M241</f>
+        <v/>
+      </c>
+      <c r="O241" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P241" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N241/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O241/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L241/'Расходы и доставка'!$B$21,T241/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q241" s="17">
+        <f>P241*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R241" s="20">
+        <f>IFERROR(Q241/L241,0)</f>
+        <v/>
+      </c>
+      <c r="S241" s="21" t="n">
+        <v>75000</v>
+      </c>
+      <c r="T241" s="17">
+        <f>L241*S241</f>
+        <v/>
+      </c>
+      <c r="U241" s="17">
+        <f>S241+R241</f>
+        <v/>
+      </c>
+      <c r="V241" s="22">
+        <f>IFERROR(R241/S241,"")</f>
+        <v/>
+      </c>
+      <c r="W241" s="16" t="inlineStr"/>
+      <c r="X241" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y241" s="23" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+        </is>
+      </c>
+      <c r="G242" s="4" t="inlineStr">
+        <is>
+          <t>521-35.2608-01</t>
+        </is>
+      </c>
+      <c r="H242" s="16" t="inlineStr"/>
+      <c r="I242" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J242" s="4" t="inlineStr"/>
+      <c r="K242" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L242" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M242" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N242" s="17">
+        <f>L242*M242</f>
+        <v/>
+      </c>
+      <c r="O242" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P242" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N242/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O242/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L242/'Расходы и доставка'!$B$21,T242/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q242" s="17">
+        <f>P242*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R242" s="20">
+        <f>IFERROR(Q242/L242,0)</f>
+        <v/>
+      </c>
+      <c r="S242" s="21" t="n"/>
+      <c r="T242" s="17">
+        <f>L242*S242</f>
+        <v/>
+      </c>
+      <c r="U242" s="17">
+        <f>S242+R242</f>
+        <v/>
+      </c>
+      <c r="V242" s="22">
+        <f>IFERROR(R242/S242,"")</f>
+        <v/>
+      </c>
+      <c r="W242" s="16" t="inlineStr"/>
+      <c r="X242" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y242" s="23" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>521-182.116</t>
+        </is>
+      </c>
+      <c r="H243" s="16" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="I243" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J243" s="4" t="inlineStr"/>
+      <c r="K243" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L243" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="N243" s="17">
+        <f>L243*M243</f>
+        <v/>
+      </c>
+      <c r="O243" s="18" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="P243" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N243/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O243/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L243/'Расходы и доставка'!$B$21,T243/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q243" s="17">
+        <f>P243*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R243" s="20">
+        <f>IFERROR(Q243/L243,0)</f>
+        <v/>
+      </c>
+      <c r="S243" s="21" t="n"/>
+      <c r="T243" s="17">
+        <f>L243*S243</f>
+        <v/>
+      </c>
+      <c r="U243" s="17">
+        <f>S243+R243</f>
+        <v/>
+      </c>
+      <c r="V243" s="22">
+        <f>IFERROR(R243/S243,"")</f>
+        <v/>
+      </c>
+      <c r="W243" s="16" t="inlineStr"/>
+      <c r="X243" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y243" s="23" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+        </is>
+      </c>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>528-35.176</t>
+        </is>
+      </c>
+      <c r="H244" s="16" t="inlineStr"/>
+      <c r="I244" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J244" s="4" t="inlineStr"/>
+      <c r="K244" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L244" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M244" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N244" s="17">
+        <f>L244*M244</f>
+        <v/>
+      </c>
+      <c r="O244" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P244" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N244/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O244/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L244/'Расходы и доставка'!$B$21,T244/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q244" s="17">
+        <f>P244*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R244" s="20">
+        <f>IFERROR(Q244/L244,0)</f>
+        <v/>
+      </c>
+      <c r="S244" s="21" t="n"/>
+      <c r="T244" s="17">
+        <f>L244*S244</f>
+        <v/>
+      </c>
+      <c r="U244" s="17">
+        <f>S244+R244</f>
+        <v/>
+      </c>
+      <c r="V244" s="22">
+        <f>IFERROR(R244/S244,"")</f>
+        <v/>
+      </c>
+      <c r="W244" s="16" t="inlineStr"/>
+      <c r="X244" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y244" s="23" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="B245" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E245" s="4" t="inlineStr"/>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>Клапан дроссельный угловой штуцерный</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>525-35.577</t>
+        </is>
+      </c>
+      <c r="H245" s="16" t="inlineStr"/>
+      <c r="I245" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J245" s="4" t="inlineStr"/>
+      <c r="K245" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L245" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N245" s="17">
+        <f>L245*M245</f>
+        <v/>
+      </c>
+      <c r="O245" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P245" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N245/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O245/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L245/'Расходы и доставка'!$B$21,T245/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q245" s="17">
+        <f>P245*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R245" s="20">
+        <f>IFERROR(Q245/L245,0)</f>
+        <v/>
+      </c>
+      <c r="S245" s="21" t="n"/>
+      <c r="T245" s="17">
+        <f>L245*S245</f>
+        <v/>
+      </c>
+      <c r="U245" s="17">
+        <f>S245+R245</f>
+        <v/>
+      </c>
+      <c r="V245" s="22">
+        <f>IFERROR(R245/S245,"")</f>
+        <v/>
+      </c>
+      <c r="W245" s="16" t="inlineStr"/>
+      <c r="X245" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y245" s="23" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="n">
+        <v>242</v>
+      </c>
+      <c r="B246" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="F246" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>521-01.493-02</t>
+        </is>
+      </c>
+      <c r="H246" s="16" t="inlineStr"/>
+      <c r="I246" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J246" s="4" t="inlineStr"/>
+      <c r="K246" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L246" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N246" s="17">
+        <f>L246*M246</f>
+        <v/>
+      </c>
+      <c r="O246" s="18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P246" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N246/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O246/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L246/'Расходы и доставка'!$B$21,T246/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q246" s="17">
+        <f>P246*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R246" s="20">
+        <f>IFERROR(Q246/L246,0)</f>
+        <v/>
+      </c>
+      <c r="S246" s="21" t="n"/>
+      <c r="T246" s="17">
+        <f>L246*S246</f>
+        <v/>
+      </c>
+      <c r="U246" s="17">
+        <f>S246+R246</f>
+        <v/>
+      </c>
+      <c r="V246" s="22">
+        <f>IFERROR(R246/S246,"")</f>
+        <v/>
+      </c>
+      <c r="W246" s="16" t="inlineStr"/>
+      <c r="X246" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y246" s="23" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="B247" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="inlineStr"/>
+      <c r="F247" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>521-03.472-01</t>
+        </is>
+      </c>
+      <c r="H247" s="16" t="inlineStr"/>
+      <c r="I247" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J247" s="4" t="inlineStr"/>
+      <c r="K247" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L247" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N247" s="17">
+        <f>L247*M247</f>
+        <v/>
+      </c>
+      <c r="O247" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P247" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N247/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O247/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L247/'Расходы и доставка'!$B$21,T247/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q247" s="17">
+        <f>P247*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R247" s="20">
+        <f>IFERROR(Q247/L247,0)</f>
+        <v/>
+      </c>
+      <c r="S247" s="21" t="n"/>
+      <c r="T247" s="17">
+        <f>L247*S247</f>
+        <v/>
+      </c>
+      <c r="U247" s="17">
+        <f>S247+R247</f>
+        <v/>
+      </c>
+      <c r="V247" s="22">
+        <f>IFERROR(R247/S247,"")</f>
+        <v/>
+      </c>
+      <c r="W247" s="16" t="inlineStr"/>
+      <c r="X247" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y247" s="23" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="B248" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="inlineStr">
+        <is>
+          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>587-35.8490-04</t>
+        </is>
+      </c>
+      <c r="H248" s="16" t="inlineStr"/>
+      <c r="I248" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J248" s="4" t="inlineStr"/>
+      <c r="K248" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M248" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N248" s="17">
+        <f>L248*M248</f>
+        <v/>
+      </c>
+      <c r="O248" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P248" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N248/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O248/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L248/'Расходы и доставка'!$B$21,T248/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q248" s="17">
+        <f>P248*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R248" s="20">
+        <f>IFERROR(Q248/L248,0)</f>
+        <v/>
+      </c>
+      <c r="S248" s="21" t="n"/>
+      <c r="T248" s="17">
+        <f>L248*S248</f>
+        <v/>
+      </c>
+      <c r="U248" s="17">
+        <f>S248+R248</f>
+        <v/>
+      </c>
+      <c r="V248" s="22">
+        <f>IFERROR(R248/S248,"")</f>
+        <v/>
+      </c>
+      <c r="W248" s="16" t="inlineStr"/>
+      <c r="X248" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y248" s="23" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr">
+        <is>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="inlineStr"/>
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>587-182.126</t>
+        </is>
+      </c>
+      <c r="H249" s="16" t="inlineStr"/>
+      <c r="I249" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J249" s="4" t="inlineStr"/>
+      <c r="K249" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L249" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M249" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N249" s="17">
+        <f>L249*M249</f>
+        <v/>
+      </c>
+      <c r="O249" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P249" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N249/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O249/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L249/'Расходы и доставка'!$B$21,T249/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q249" s="17">
+        <f>P249*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R249" s="20">
+        <f>IFERROR(Q249/L249,0)</f>
+        <v/>
+      </c>
+      <c r="S249" s="21" t="n"/>
+      <c r="T249" s="17">
+        <f>L249*S249</f>
+        <v/>
+      </c>
+      <c r="U249" s="17">
+        <f>S249+R249</f>
+        <v/>
+      </c>
+      <c r="V249" s="22">
+        <f>IFERROR(R249/S249,"")</f>
+        <v/>
+      </c>
+      <c r="W249" s="16" t="inlineStr"/>
+      <c r="X249" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y249" s="23" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="n">
+        <v>246</v>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="inlineStr"/>
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>Клапан фреоновый саленоидный</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr"/>
+      <c r="H250" s="16" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="I250" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J250" s="4" t="inlineStr"/>
+      <c r="K250" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L250" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M250" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N250" s="17">
+        <f>L250*M250</f>
+        <v/>
+      </c>
+      <c r="O250" s="18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P250" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N250/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O250/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L250/'Расходы и доставка'!$B$21,T250/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q250" s="17">
+        <f>P250*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R250" s="20">
+        <f>IFERROR(Q250/L250,0)</f>
+        <v/>
+      </c>
+      <c r="S250" s="21" t="n"/>
+      <c r="T250" s="17">
+        <f>L250*S250</f>
+        <v/>
+      </c>
+      <c r="U250" s="17">
+        <f>S250+R250</f>
+        <v/>
+      </c>
+      <c r="V250" s="22">
+        <f>IFERROR(R250/S250,"")</f>
+        <v/>
+      </c>
+      <c r="W250" s="16" t="inlineStr"/>
+      <c r="X250" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y250" s="23" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="F251" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="K230" s="24">
-        <f>SUM(K5:K229)</f>
-        <v/>
-      </c>
-      <c r="L230" s="24">
-        <f>SUM(L5:L229)</f>
-        <v/>
-      </c>
-      <c r="N230" s="24">
-        <f>SUM(N5:N229)</f>
-        <v/>
-      </c>
-      <c r="O230" s="25">
-        <f>SUM(O5:O229)</f>
-        <v/>
-      </c>
-      <c r="Q230" s="24">
-        <f>SUM(Q5:Q229)</f>
-        <v/>
-      </c>
-      <c r="T230" s="24">
-        <f>SUM(T5:T229)</f>
+      <c r="K251" s="24">
+        <f>SUM(K5:K250)</f>
+        <v/>
+      </c>
+      <c r="L251" s="24">
+        <f>SUM(L5:L250)</f>
+        <v/>
+      </c>
+      <c r="N251" s="24">
+        <f>SUM(N5:N250)</f>
+        <v/>
+      </c>
+      <c r="O251" s="25">
+        <f>SUM(O5:O250)</f>
+        <v/>
+      </c>
+      <c r="Q251" s="24">
+        <f>SUM(Q5:Q250)</f>
+        <v/>
+      </c>
+      <c r="T251" s="24">
+        <f>SUM(T5:T250)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Y229"/>
+  <autoFilter ref="A4:Y250"/>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H229" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Новое,Б/у,Восстановленное"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I229" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Комплект,Не комплект,Брак"</formula1>
     </dataValidation>
   </dataValidations>
@@ -21798,23 +23662,23 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF('Отгрузка'!H$5:H$229,"Новое")</f>
+        <f>COUNTIF('Отгрузка'!H$5:H$250,"Новое")</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Новое",'Отгрузка'!L$5:L$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Новое",'Отгрузка'!L$5:L$250)</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Новое",'Отгрузка'!N$5:N$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Новое",'Отгрузка'!N$5:N$250)</f>
         <v/>
       </c>
       <c r="E5" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Новое",'Отгрузка'!T$5:T$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Новое",'Отгрузка'!T$5:T$250)</f>
         <v/>
       </c>
       <c r="F5" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Новое",'Отгрузка'!Q$5:Q$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Новое",'Отгрузка'!Q$5:Q$250)</f>
         <v/>
       </c>
       <c r="G5" s="26">
@@ -21829,23 +23693,23 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF('Отгрузка'!H$5:H$229,"Б/у")</f>
+        <f>COUNTIF('Отгрузка'!H$5:H$250,"Б/у")</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Б/у",'Отгрузка'!L$5:L$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Б/у",'Отгрузка'!L$5:L$250)</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Б/у",'Отгрузка'!N$5:N$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Б/у",'Отгрузка'!N$5:N$250)</f>
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Б/у",'Отгрузка'!T$5:T$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Б/у",'Отгрузка'!T$5:T$250)</f>
         <v/>
       </c>
       <c r="F6" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Б/у",'Отгрузка'!Q$5:Q$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Б/у",'Отгрузка'!Q$5:Q$250)</f>
         <v/>
       </c>
       <c r="G6" s="26">
@@ -21860,23 +23724,23 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF('Отгрузка'!H$5:H$229,"Восстановленное")</f>
+        <f>COUNTIF('Отгрузка'!H$5:H$250,"Восстановленное")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Восстановленное",'Отгрузка'!L$5:L$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Восстановленное",'Отгрузка'!L$5:L$250)</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Восстановленное",'Отгрузка'!N$5:N$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Восстановленное",'Отгрузка'!N$5:N$250)</f>
         <v/>
       </c>
       <c r="E7" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Восстановленное",'Отгрузка'!T$5:T$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Восстановленное",'Отгрузка'!T$5:T$250)</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"Восстановленное",'Отгрузка'!Q$5:Q$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"Восстановленное",'Отгрузка'!Q$5:Q$250)</f>
         <v/>
       </c>
       <c r="G7" s="26">
@@ -21891,23 +23755,23 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTBLANK('Отгрузка'!H$5:H$229)</f>
+        <f>COUNTBLANK('Отгрузка'!H$5:H$250)</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"",'Отгрузка'!L$5:L$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"",'Отгрузка'!L$5:L$250)</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"",'Отгрузка'!N$5:N$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"",'Отгрузка'!N$5:N$250)</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"",'Отгрузка'!T$5:T$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"",'Отгрузка'!T$5:T$250)</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$229,"",'Отгрузка'!Q$5:Q$229)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$250,"",'Отгрузка'!Q$5:Q$250)</f>
         <v/>
       </c>
       <c r="G8" s="26">
@@ -21960,7 +23824,7 @@
         </is>
       </c>
       <c r="B12" s="24">
-        <f>SUM('Отгрузка'!Q$5:Q$229)</f>
+        <f>SUM('Отгрузка'!Q$5:Q$250)</f>
         <v/>
       </c>
     </row>
@@ -21982,7 +23846,7 @@
         </is>
       </c>
       <c r="B14" s="24">
-        <f>SUM('Отгрузка'!Q$5:Q$229)-'Расходы и доставка'!$B$13</f>
+        <f>SUM('Отгрузка'!Q$5:Q$250)-'Расходы и доставка'!$B$13</f>
         <v/>
       </c>
     </row>
